--- a/Team-Data/2007-08/4-11-2007-08.xlsx
+++ b/Team-Data/2007-08/4-11-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E2" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2" t="n">
         <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>0.468</v>
+        <v>0.462</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -679,19 +746,19 @@
         <v>36.2</v>
       </c>
       <c r="J2" t="n">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M2" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="N2" t="n">
-        <v>0.36</v>
+        <v>0.356</v>
       </c>
       <c r="O2" t="n">
         <v>21.1</v>
@@ -703,7 +770,7 @@
         <v>0.774</v>
       </c>
       <c r="R2" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S2" t="n">
         <v>30</v>
@@ -712,34 +779,34 @@
         <v>42.3</v>
       </c>
       <c r="U2" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="V2" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X2" t="n">
         <v>5.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.2</v>
+        <v>98</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
         <v>18</v>
@@ -757,7 +824,7 @@
         <v>21</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
         <v>16</v>
@@ -766,10 +833,10 @@
         <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO2" t="n">
         <v>5</v>
@@ -802,7 +869,7 @@
         <v>4</v>
       </c>
       <c r="AY2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F3" t="n">
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.797</v>
+        <v>0.795</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>76.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="K3" t="n">
         <v>0.475</v>
@@ -870,16 +937,16 @@
         <v>7.3</v>
       </c>
       <c r="M3" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="O3" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="P3" t="n">
-        <v>26.5</v>
+        <v>26.7</v>
       </c>
       <c r="Q3" t="n">
         <v>0.77</v>
@@ -888,13 +955,13 @@
         <v>10.1</v>
       </c>
       <c r="S3" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T3" t="n">
         <v>42</v>
       </c>
       <c r="U3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V3" t="n">
         <v>15.3</v>
@@ -912,16 +979,16 @@
         <v>22.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB3" t="n">
         <v>100.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,28 +1012,28 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
         <v>12</v>
       </c>
       <c r="AN3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO3" t="n">
         <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
         <v>24</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT3" t="n">
         <v>14</v>
@@ -993,7 +1060,7 @@
         <v>8</v>
       </c>
       <c r="BB3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>-4.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF4" t="n">
         <v>23</v>
@@ -1115,7 +1182,7 @@
         <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
         <v>25</v>
@@ -1127,22 +1194,22 @@
         <v>17</v>
       </c>
       <c r="AL4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>20</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
@@ -1154,13 +1221,13 @@
         <v>26</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
         <v>14</v>
@@ -1172,7 +1239,7 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
         <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>0.392</v>
+        <v>0.385</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1225,28 +1292,28 @@
         <v>36.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K5" t="n">
         <v>0.432</v>
       </c>
       <c r="L5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M5" t="n">
         <v>15.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.365</v>
+        <v>0.364</v>
       </c>
       <c r="O5" t="n">
         <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="R5" t="n">
         <v>12.9</v>
@@ -1261,13 +1328,13 @@
         <v>21.8</v>
       </c>
       <c r="V5" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="W5" t="n">
         <v>7.7</v>
       </c>
       <c r="X5" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
         <v>5.7</v>
@@ -1282,10 +1349,10 @@
         <v>96.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.3</v>
+        <v>-3.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1300,7 +1367,7 @@
         <v>13</v>
       </c>
       <c r="AI5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1318,16 +1385,16 @@
         <v>14</v>
       </c>
       <c r="AO5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ5" t="n">
         <v>17</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS5" t="n">
         <v>18</v>
@@ -1336,7 +1403,7 @@
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV5" t="n">
         <v>17</v>
@@ -1357,7 +1424,7 @@
         <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E6" t="n">
         <v>43</v>
       </c>
       <c r="F6" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>0.544</v>
+        <v>0.551</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1422,22 +1489,22 @@
         <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.718</v>
+        <v>0.72</v>
       </c>
       <c r="R6" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S6" t="n">
         <v>31.2</v>
       </c>
       <c r="T6" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U6" t="n">
         <v>20.1</v>
@@ -1452,22 +1519,22 @@
         <v>5.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB6" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1482,13 +1549,13 @@
         <v>4</v>
       </c>
       <c r="AI6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ6" t="n">
         <v>13</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>14</v>
@@ -1497,13 +1564,13 @@
         <v>13</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO6" t="n">
         <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
@@ -1515,7 +1582,7 @@
         <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
         <v>24</v>
@@ -1527,7 +1594,7 @@
         <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
         <v>14</v>
@@ -1536,13 +1603,13 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB6" t="n">
         <v>18</v>
       </c>
       <c r="BC6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>9</v>
@@ -1661,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1679,7 +1746,7 @@
         <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO7" t="n">
         <v>7</v>
@@ -1700,7 +1767,7 @@
         <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV7" t="n">
         <v>5</v>
@@ -1709,7 +1776,7 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
@@ -1724,7 +1791,7 @@
         <v>13</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
         <v>3</v>
@@ -1861,7 +1928,7 @@
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -1935,28 +2002,28 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
         <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>0.709</v>
+        <v>0.705</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L9" t="n">
         <v>6</v>
@@ -1965,13 +2032,13 @@
         <v>16.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.366</v>
+        <v>0.368</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q9" t="n">
         <v>0.765</v>
@@ -1980,10 +2047,10 @@
         <v>11.9</v>
       </c>
       <c r="S9" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T9" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U9" t="n">
         <v>22.4</v>
@@ -1995,7 +2062,7 @@
         <v>7.2</v>
       </c>
       <c r="X9" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y9" t="n">
         <v>3.9</v>
@@ -2007,13 +2074,13 @@
         <v>19.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2031,22 +2098,22 @@
         <v>18</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
       </c>
       <c r="AL9" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO9" t="n">
         <v>18</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>19</v>
       </c>
       <c r="AP9" t="n">
         <v>20</v>
@@ -2055,22 +2122,22 @@
         <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS9" t="n">
         <v>25</v>
       </c>
       <c r="AT9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
         <v>3</v>
@@ -2079,16 +2146,16 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>12</v>
@@ -2207,7 +2274,7 @@
         <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>2</v>
@@ -2231,7 +2298,7 @@
         <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -2299,46 +2366,46 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F11" t="n">
         <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
       </c>
       <c r="I11" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J11" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M11" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N11" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O11" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
         <v>22.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
       <c r="R11" t="n">
         <v>12.2</v>
@@ -2353,7 +2420,7 @@
         <v>21.4</v>
       </c>
       <c r="V11" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W11" t="n">
         <v>7.3</v>
@@ -2374,10 +2441,10 @@
         <v>96.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2392,13 +2459,13 @@
         <v>25</v>
       </c>
       <c r="AI11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ11" t="n">
         <v>15</v>
       </c>
       <c r="AK11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL11" t="n">
         <v>10</v>
@@ -2416,7 +2483,7 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
         <v>8</v>
@@ -2437,22 +2504,22 @@
         <v>15</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
         <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F12" t="n">
         <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>0.443</v>
+        <v>0.436</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2508,25 +2575,25 @@
         <v>9.1</v>
       </c>
       <c r="M12" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.371</v>
+        <v>0.373</v>
       </c>
       <c r="O12" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>24.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R12" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
         <v>43.2</v>
@@ -2541,7 +2608,7 @@
         <v>7.7</v>
       </c>
       <c r="X12" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
         <v>5.1</v>
@@ -2550,16 +2617,16 @@
         <v>23.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.6</v>
+        <v>103.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
         <v>20</v>
@@ -2589,16 +2656,16 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2616,7 +2683,7 @@
         <v>26</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
         <v>11</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>29</v>
@@ -2777,7 +2844,7 @@
         <v>6</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
         <v>6</v>
@@ -2804,10 +2871,10 @@
         <v>13</v>
       </c>
       <c r="AY13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" t="n">
         <v>25</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H14" t="n">
         <v>48.3</v>
@@ -2863,37 +2930,37 @@
         <v>39.6</v>
       </c>
       <c r="J14" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
       </c>
       <c r="L14" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O14" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P14" t="n">
         <v>27.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R14" t="n">
         <v>10.9</v>
       </c>
       <c r="S14" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T14" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
         <v>24.3</v>
@@ -2911,7 +2978,7 @@
         <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA14" t="n">
         <v>22.6</v>
@@ -2926,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
@@ -2935,7 +3002,7 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI14" t="n">
         <v>5</v>
@@ -2950,10 +3017,10 @@
         <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,7 +3029,7 @@
         <v>5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>19</v>
@@ -2989,7 +3056,7 @@
         <v>13</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" t="n">
         <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>0.278</v>
+        <v>0.269</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
@@ -3057,16 +3124,16 @@
         <v>21.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O15" t="n">
         <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.728</v>
+        <v>0.73</v>
       </c>
       <c r="R15" t="n">
         <v>10.2</v>
@@ -3075,43 +3142,43 @@
         <v>31.2</v>
       </c>
       <c r="T15" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y15" t="n">
         <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
         <v>22.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3132,28 +3199,28 @@
         <v>7</v>
       </c>
       <c r="AM15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
         <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
       </c>
       <c r="AT15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU15" t="n">
         <v>29</v>
@@ -3165,16 +3232,16 @@
         <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
         <v>18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E16" t="n">
         <v>14</v>
       </c>
       <c r="F16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>0.177</v>
+        <v>0.179</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,67 +3294,67 @@
         <v>34.3</v>
       </c>
       <c r="J16" t="n">
-        <v>77.2</v>
+        <v>77</v>
       </c>
       <c r="K16" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L16" t="n">
         <v>5.8</v>
       </c>
       <c r="M16" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O16" t="n">
         <v>17.1</v>
       </c>
       <c r="P16" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R16" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="S16" t="n">
         <v>28.6</v>
       </c>
       <c r="T16" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="U16" t="n">
         <v>20</v>
       </c>
       <c r="V16" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
         <v>7.2</v>
       </c>
       <c r="X16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Z16" t="n">
         <v>20.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB16" t="n">
         <v>91.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3314,7 +3381,7 @@
         <v>22</v>
       </c>
       <c r="AM16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN16" t="n">
         <v>18</v>
@@ -3326,7 +3393,7 @@
         <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3350,7 +3417,7 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" t="n">
         <v>26</v>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>0.329</v>
+        <v>0.333</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3412,25 +3479,25 @@
         <v>82.2</v>
       </c>
       <c r="K17" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
       </c>
       <c r="M17" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O17" t="n">
         <v>17.6</v>
       </c>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.735</v>
+        <v>0.736</v>
       </c>
       <c r="R17" t="n">
         <v>12.9</v>
@@ -3457,19 +3524,19 @@
         <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AA17" t="n">
         <v>21</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.7</v>
+        <v>-6.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
@@ -3484,13 +3551,13 @@
         <v>8</v>
       </c>
       <c r="AI17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL17" t="n">
         <v>24</v>
@@ -3511,7 +3578,7 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS17" t="n">
         <v>29</v>
@@ -3520,10 +3587,10 @@
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV17" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
@@ -3532,16 +3599,16 @@
         <v>20</v>
       </c>
       <c r="AY17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
         <v>26</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
         <v>59</v>
       </c>
       <c r="G18" t="n">
-        <v>0.253</v>
+        <v>0.244</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3603,7 +3670,7 @@
         <v>15.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
         <v>15.2</v>
@@ -3612,19 +3679,19 @@
         <v>20.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="R18" t="n">
         <v>11.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="U18" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V18" t="n">
         <v>14.6</v>
@@ -3633,7 +3700,7 @@
         <v>7.5</v>
       </c>
       <c r="X18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
         <v>5.7</v>
@@ -3645,13 +3712,13 @@
         <v>17.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.1</v>
+        <v>-7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
         <v>28</v>
@@ -3672,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
@@ -3681,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
         <v>30</v>
@@ -3708,7 +3775,7 @@
         <v>18</v>
       </c>
       <c r="AW18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3723,7 +3790,7 @@
         <v>30</v>
       </c>
       <c r="BB18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E19" t="n">
         <v>32</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G19" t="n">
-        <v>0.405</v>
+        <v>0.41</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
@@ -3782,19 +3849,19 @@
         <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P19" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.733</v>
+        <v>0.734</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
@@ -3803,7 +3870,7 @@
         <v>30.8</v>
       </c>
       <c r="T19" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U19" t="n">
         <v>23.2</v>
@@ -3818,22 +3885,22 @@
         <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA19" t="n">
         <v>22.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.3</v>
+        <v>-5</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
         <v>21</v>
@@ -3857,13 +3924,13 @@
         <v>26</v>
       </c>
       <c r="AL19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM19" t="n">
         <v>18</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3893,7 +3960,7 @@
         <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
@@ -3902,7 +3969,7 @@
         <v>26</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
         <v>55</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" t="n">
-        <v>0.696</v>
+        <v>0.705</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3967,10 +4034,10 @@
         <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.392</v>
+        <v>0.391</v>
       </c>
       <c r="O20" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P20" t="n">
         <v>20.7</v>
@@ -3979,13 +4046,13 @@
         <v>0.767</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S20" t="n">
         <v>30.4</v>
       </c>
       <c r="T20" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
@@ -4003,7 +4070,7 @@
         <v>4.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA20" t="n">
         <v>19.2</v>
@@ -4012,19 +4079,19 @@
         <v>100.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="n">
         <v>13</v>
@@ -4033,7 +4100,7 @@
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
         <v>8</v>
@@ -4054,19 +4121,19 @@
         <v>28</v>
       </c>
       <c r="AQ20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR20" t="n">
         <v>13</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>14</v>
       </c>
       <c r="AS20" t="n">
         <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -4119,25 +4186,25 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E21" t="n">
         <v>23</v>
       </c>
       <c r="F21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21" t="n">
-        <v>0.288</v>
+        <v>0.291</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
       </c>
       <c r="I21" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.44</v>
@@ -4149,19 +4216,19 @@
         <v>17.5</v>
       </c>
       <c r="N21" t="n">
-        <v>0.337</v>
+        <v>0.336</v>
       </c>
       <c r="O21" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P21" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R21" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S21" t="n">
         <v>29.9</v>
@@ -4188,13 +4255,13 @@
         <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
@@ -4203,22 +4270,22 @@
         <v>25</v>
       </c>
       <c r="AF21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
         <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>21</v>
@@ -4230,10 +4297,10 @@
         <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>25</v>
@@ -4242,7 +4309,7 @@
         <v>6</v>
       </c>
       <c r="AS21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT21" t="n">
         <v>10</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ21" t="n">
         <v>18</v>
@@ -4269,7 +4336,7 @@
         <v>20</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -4301,22 +4368,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E22" t="n">
         <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" t="n">
-        <v>0.62</v>
+        <v>0.628</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
       </c>
       <c r="I22" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J22" t="n">
         <v>78.59999999999999</v>
@@ -4331,25 +4398,25 @@
         <v>25.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.385</v>
+        <v>0.384</v>
       </c>
       <c r="O22" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="P22" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.722</v>
+        <v>0.724</v>
       </c>
       <c r="R22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="S22" t="n">
         <v>32.7</v>
       </c>
       <c r="T22" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U22" t="n">
         <v>20.5</v>
@@ -4367,10 +4434,10 @@
         <v>4.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AB22" t="n">
         <v>104.3</v>
@@ -4379,13 +4446,13 @@
         <v>5</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE22" t="n">
         <v>10</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG22" t="n">
         <v>10</v>
@@ -4415,7 +4482,7 @@
         <v>9</v>
       </c>
       <c r="AP22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ22" t="n">
         <v>27</v>
@@ -4439,13 +4506,13 @@
         <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
         <v>40</v>
       </c>
       <c r="F23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G23" t="n">
-        <v>0.506</v>
+        <v>0.513</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,37 +4568,37 @@
         <v>37.2</v>
       </c>
       <c r="J23" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.459</v>
+        <v>0.461</v>
       </c>
       <c r="L23" t="n">
         <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0.313</v>
+        <v>0.317</v>
       </c>
       <c r="O23" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="P23" t="n">
         <v>26.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.707</v>
+        <v>0.71</v>
       </c>
       <c r="R23" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="S23" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U23" t="n">
         <v>20.4</v>
@@ -4540,7 +4607,7 @@
         <v>14.4</v>
       </c>
       <c r="W23" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X23" t="n">
         <v>5</v>
@@ -4549,19 +4616,19 @@
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>15</v>
@@ -4582,7 +4649,7 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4594,13 +4661,13 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR23" t="n">
         <v>2</v>
@@ -4609,31 +4676,31 @@
         <v>28</v>
       </c>
       <c r="AT23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU23" t="n">
         <v>23</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>4</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -4665,40 +4732,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E24" t="n">
         <v>53</v>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G24" t="n">
-        <v>0.663</v>
+        <v>0.671</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>0.501</v>
       </c>
       <c r="L24" t="n">
         <v>8.5</v>
       </c>
       <c r="M24" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N24" t="n">
         <v>0.394</v>
       </c>
       <c r="O24" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P24" t="n">
         <v>23.9</v>
@@ -4716,13 +4783,13 @@
         <v>41.2</v>
       </c>
       <c r="U24" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="V24" t="n">
         <v>14.4</v>
       </c>
       <c r="W24" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X24" t="n">
         <v>6.4</v>
@@ -4737,16 +4804,16 @@
         <v>21</v>
       </c>
       <c r="AB24" t="n">
-        <v>110.1</v>
+        <v>110.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AD24" t="n">
         <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF24" t="n">
         <v>7</v>
@@ -4755,13 +4822,13 @@
         <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4773,7 +4840,7 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="n">
         <v>14</v>
@@ -4797,7 +4864,7 @@
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
         <v>22</v>
@@ -4809,7 +4876,7 @@
         <v>2</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>15</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E25" t="n">
         <v>39</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G25" t="n">
-        <v>0.494</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
@@ -4877,22 +4944,22 @@
         <v>17.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O25" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R25" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S25" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T25" t="n">
         <v>40.8</v>
@@ -4907,7 +4974,7 @@
         <v>5.5</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
         <v>3.7</v>
@@ -4919,22 +4986,22 @@
         <v>20.3</v>
       </c>
       <c r="AB25" t="n">
-        <v>95</v>
+        <v>95.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH25" t="n">
         <v>1</v>
@@ -4943,19 +5010,19 @@
         <v>27</v>
       </c>
       <c r="AJ25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="n">
         <v>24</v>
@@ -4964,7 +5031,7 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AR25" t="n">
         <v>18</v>
@@ -4973,7 +5040,7 @@
         <v>22</v>
       </c>
       <c r="AT25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU25" t="n">
         <v>19</v>
@@ -4985,19 +5052,19 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
       </c>
       <c r="AZ25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
         <v>21</v>
       </c>
       <c r="BB25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -5029,43 +5096,43 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F26" t="n">
         <v>42</v>
       </c>
       <c r="G26" t="n">
-        <v>0.468</v>
+        <v>0.462</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J26" t="n">
         <v>80</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.462</v>
       </c>
       <c r="L26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.373</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="P26" t="n">
-        <v>27.9</v>
+        <v>28.1</v>
       </c>
       <c r="Q26" t="n">
         <v>0.799</v>
@@ -5095,19 +5162,19 @@
         <v>5.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AB26" t="n">
         <v>102.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5137,25 +5204,25 @@
         <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU26" t="n">
         <v>28</v>
@@ -5167,7 +5234,7 @@
         <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY26" t="n">
         <v>27</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E27" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F27" t="n">
         <v>25</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
       </c>
       <c r="I27" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J27" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L27" t="n">
         <v>7.3</v>
@@ -5241,28 +5308,28 @@
         <v>19.7</v>
       </c>
       <c r="N27" t="n">
-        <v>0.369</v>
+        <v>0.371</v>
       </c>
       <c r="O27" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P27" t="n">
         <v>21.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.763</v>
+        <v>0.765</v>
       </c>
       <c r="R27" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S27" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U27" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="V27" t="n">
         <v>12.7</v>
@@ -5271,13 +5338,13 @@
         <v>6.3</v>
       </c>
       <c r="X27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y27" t="n">
         <v>4.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA27" t="n">
         <v>19.9</v>
@@ -5286,10 +5353,10 @@
         <v>95.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE27" t="n">
         <v>5</v>
@@ -5313,7 +5380,7 @@
         <v>15</v>
       </c>
       <c r="AL27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM27" t="n">
         <v>9</v>
@@ -5322,7 +5389,7 @@
         <v>11</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
@@ -5331,16 +5398,16 @@
         <v>15</v>
       </c>
       <c r="AR27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV27" t="n">
         <v>4</v>
@@ -5352,7 +5419,7 @@
         <v>24</v>
       </c>
       <c r="AY27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ27" t="n">
         <v>2</v>
@@ -5364,7 +5431,7 @@
         <v>26</v>
       </c>
       <c r="BC27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E28" t="n">
         <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G28" t="n">
-        <v>0.225</v>
+        <v>0.228</v>
       </c>
       <c r="H28" t="n">
         <v>48.4</v>
@@ -5411,46 +5478,46 @@
         <v>38</v>
       </c>
       <c r="J28" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L28" t="n">
         <v>3.9</v>
       </c>
       <c r="M28" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.334</v>
+        <v>0.333</v>
       </c>
       <c r="O28" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.769</v>
+        <v>0.77</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S28" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T28" t="n">
         <v>44.5</v>
       </c>
       <c r="U28" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V28" t="n">
         <v>16.1</v>
       </c>
       <c r="W28" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X28" t="n">
         <v>4.9</v>
@@ -5462,13 +5529,13 @@
         <v>20.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.2</v>
+        <v>97.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>-9.1</v>
+        <v>-8.9</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -5510,19 +5577,19 @@
         <v>24</v>
       </c>
       <c r="AQ28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR28" t="n">
         <v>10</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AV28" t="n">
         <v>30</v>
@@ -5537,13 +5604,13 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
         <v>30</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F29" t="n">
         <v>39</v>
       </c>
       <c r="G29" t="n">
-        <v>0.506</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5608,10 +5675,10 @@
         <v>0.394</v>
       </c>
       <c r="O29" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P29" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="Q29" t="n">
         <v>0.8129999999999999</v>
@@ -5620,10 +5687,10 @@
         <v>9.6</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="U29" t="n">
         <v>23.8</v>
@@ -5635,7 +5702,7 @@
         <v>6.9</v>
       </c>
       <c r="X29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
         <v>4</v>
@@ -5644,25 +5711,25 @@
         <v>19.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>100.5</v>
+        <v>100.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH29" t="n">
         <v>8</v>
@@ -5671,22 +5738,22 @@
         <v>7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK29" t="n">
         <v>7</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP29" t="n">
         <v>30</v>
@@ -5695,13 +5762,13 @@
         <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS29" t="n">
         <v>14</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>5</v>
@@ -5713,10 +5780,10 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ29" t="n">
         <v>5</v>
@@ -5725,7 +5792,7 @@
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>7.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
       </c>
       <c r="AF30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG30" t="n">
         <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
         <v>4</v>
@@ -5871,19 +5938,19 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AQ30" t="n">
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5898,7 +5965,7 @@
         <v>23</v>
       </c>
       <c r="AY30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
@@ -5910,7 +5977,7 @@
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
         <v>41</v>
       </c>
       <c r="F31" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" t="n">
-        <v>0.519</v>
+        <v>0.526</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J31" t="n">
         <v>81.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.448</v>
       </c>
       <c r="L31" t="n">
         <v>6.9</v>
@@ -5969,13 +6036,13 @@
         <v>19.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="O31" t="n">
         <v>19.2</v>
       </c>
       <c r="P31" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.787</v>
@@ -5984,13 +6051,13 @@
         <v>12.1</v>
       </c>
       <c r="S31" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="T31" t="n">
         <v>41.3</v>
       </c>
       <c r="U31" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V31" t="n">
         <v>13.2</v>
@@ -6002,7 +6069,7 @@
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z31" t="n">
         <v>19.6</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6032,13 +6099,13 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
         <v>16</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL31" t="n">
         <v>13</v>
@@ -6047,7 +6114,7 @@
         <v>10</v>
       </c>
       <c r="AN31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
@@ -6080,7 +6147,7 @@
         <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>6</v>
@@ -6092,7 +6159,7 @@
         <v>14</v>
       </c>
       <c r="BC31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-11-2007-08</t>
+          <t>2008-04-11</t>
         </is>
       </c>
     </row>
